--- a/BOM02_J2.xlsx
+++ b/BOM02_J2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\booksmakers_engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CF71E5-C0E1-44D9-9E08-A2862A0F902E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C642EF24-FC8C-4C11-9CEB-E7FD9A8EEF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8F4F8EA3-C038-45D0-B3C7-7FE091B94CA1}"/>
   </bookViews>
@@ -301,7 +301,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,6 +323,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,7 +415,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -462,6 +468,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -862,22 +874,22 @@
       <c r="D3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="19" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="9" t="s">
